--- a/2022 data/excel_outputs/237_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/237_boothwise_data.xlsx
@@ -14,657 +14,1329 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="463">
   <si>
     <t>AC 237 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>##### ##### ##### ####### #### #####.1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### #####.2</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### #####.3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### #####.4</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ####### #### ##.1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ####### #### ##.#</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####.3</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####.4</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### ## .1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ##### #### ##### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ##### #### ##### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######### #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######### #### ## 3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ##.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ###### ### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ###### ### #### ##.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ##### ##### #### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### #### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### #### #### ##.3</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #########</t>
-  </si>
-  <si>
-    <t>######## ######## ########### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ########### #### #####.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ## ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### #### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### #### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##########</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### #####.3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### #### #####.2</t>
-  </si>
-  <si>
-    <t>###### ##### ### ########### ## #### ## #</t>
-  </si>
-  <si>
-    <t>###### ##### ### ########### ## #### ## 2</t>
-  </si>
-  <si>
-    <t>###### ##### ### ########### ## #### ## 3</t>
-  </si>
-  <si>
-    <t>###### ##### ### ########### ## #### ## 4</t>
-  </si>
-  <si>
-    <t>###### ##### ### ########### ## #### ## 5</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ##### ## #### ## 1</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ##### ## #### ## 2</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ##### ## #### ##.3</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ##### ## #### ##. 4</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ##### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ##### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ##</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### ## 2</t>
-  </si>
-  <si>
-    <t>###### ### ###### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ##### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##########</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ##.2</t>
-  </si>
-  <si>
-    <t>##### #### ######## ######## #### #### #####.1</t>
-  </si>
-  <si>
-    <t>##### #### ######## ######## #### #### #####.2</t>
-  </si>
-  <si>
-    <t>##### #### ######## ######## #### #### #####.3</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ########</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ####### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ####### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #######</t>
-  </si>
-  <si>
-    <t>###### ####### ##### ##### ####### #### ##.1</t>
-  </si>
-  <si>
-    <t>###### ####### ##### ##### ####### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ########### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ## ##### #### ####</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### ## 1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### ## #</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### ## 3</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##.2</t>
-  </si>
-  <si>
-    <t>##### #### ######## ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ##### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #######</t>
-  </si>
-  <si>
-    <t>##### #### #### ######## ######## ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>##### #### #### ######## ######## ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>##### #### #### ######## ######## ###### #### #####.3</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ######</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### #### ## #</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### #### ## 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### #### ## 4</t>
-  </si>
-  <si>
-    <t>######## ######## #### ## ##### ##### ##### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ### #### ## #</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ###### #### ## #</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ### #### ## ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ## ##### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ## #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ## #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##</t>
-  </si>
-  <si>
-    <t>######## ######## ### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #####.3</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ## 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### #### #####.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ## ##### #### ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ## ##### #### ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ##########</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###########</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### #########</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######## #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######## #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### #### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ###### #### #####.3</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ##.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ##.2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######## #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######## #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #########</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #########</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### #### #########</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ######## #### ## #</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ######## #### ## 3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ######## #### ## 4</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ##### #### ## #</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ###.2 #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ###.2 #### #####.2</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ########</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###### #### #####.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###### #### #####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######## #### #####.1</t>
+    <t>TULASI I TAR KALEJ RAJAPUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>TULASI I TAR KALEJ RAJAPUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>TULASI I TAR KALEJ RAJAPUR KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>RAJAK Y BA LAKA I TAR KALEJ RAJAPARU KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>RAJAK Y BA LAKA I TAR KALEJ RAJAPARU KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>RAJAK Y BA LAKA I TAR KALEJ RAJAPARU KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>RAJAK Y BA LAKA I TAR KALEJ RAJAPARU KAMARA NAM0-4</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAJAPUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAJAPUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAJAPUR KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAJAPUR KAMARA NAM0-4</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHATAVARA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHATAVARA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MALAVARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PARAKO</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY SOTI PARU VA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY SOTI PARU VA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NA DAN KU MAYAN KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NA DAN KU MAYAN KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NA DAN KU MAYAN KAMARA N0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BENAURA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY CHORAHA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY BHABHET</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAGAUL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY (PAUL'</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY (PAUL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHADE VARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AMAVॉ NAYA BHAVAN</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AMAN</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY SAKAR'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAYA BHAVAN KARAUDASH KALA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAYA BHAVAN KARAUDASH KALA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAMHAPUR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GHUREHATA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAJU.RAHA KALॉ KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAJU.RAHA KALॉ KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAJU-RAHA KHUD</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AMARAPUR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAY-RAYA MAPH</t>
+  </si>
+  <si>
+    <t>GODHVAMI I TAR KALEJ CH1B2 KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>GODHVAMI I TAR KALEJ CH1B2 KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH1B2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NONAGAR PURAVA MAJARA ATARASURI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GOBARAUL</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TIRAMAU</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SHAVALAHA PURAVA MAJARA B(VA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY B(VA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GAMJ MAJARA B(VA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SARAVAL MAPH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAKARA MAJARA SARAVAL MAPH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KATAI YA KHADAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARACH1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SUHEL</t>
+  </si>
+  <si>
+    <t>K6YA TH MAK V YALAY H6NA7BANAIKA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY H6NA7BANAIKA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY B8HAURA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY UPHARAUL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B-RAYA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAKABHADESAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAPARAUD</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DADAR'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HATAVA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SURAUDHA NAVIN</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY M TAYARA KA PARU VA MAJARA DHADHAVAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KOPA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKAR=</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKHAUHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAKAUR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RE DI BHUSAUL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BASARE H'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY 7BAYAVAL KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY 7BAYAVAL KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KASHINATH KA PARU VA MAJARA 7BAYAVAL</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TADI</t>
+  </si>
+  <si>
+    <t>TH MAK V YALAY CHAKALAIYA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAVAR</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY MAVAI KALॉ KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY MAVAI KALॉ KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY MAVAI KALॉ KAMARA N0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY M DAUR KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY M DAUR KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAB U AR'</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS JBH|LABHJBH|CHAJDY</t>
+  </si>
+  <si>
+    <t>KL|AIBHT|JBH|THABH J~NAKL|AIBHTBBH SHR AIKL|PKL|AI SHRCH|JBH|THABHKL|SHRAKL|SHRCH|KL AIBHTBBHDYAJ8JBH|THABHBBH|SHRAKL|M</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY A HARASH KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY A HARASH KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY @CHAVAL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAIDANA MAJARA MAU</t>
+  </si>
+  <si>
+    <t>MAHAM@T AN NATH MAHA V YALAY KAMARA NAM0 1 MAU</t>
+  </si>
+  <si>
+    <t>MAHAM@T AN NATH MAHA V YALAY KAMARA NAM0 2 MAU</t>
+  </si>
+  <si>
+    <t>MAHAM@T AN NATH MAHA V YALAY KAMARA NAM0 3 MAU</t>
+  </si>
+  <si>
+    <t>MAHAM@T AN NATH MAHA V YALAY KAMARA NAM0 4 MAU</t>
+  </si>
+  <si>
+    <t>MAHAM@T AN NATH MAHA V YALAY KAMARA NAM0 5 MAU</t>
+  </si>
+  <si>
+    <t>PANIDAT PURUSHOTTAM INTAR KALEJ MAU KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PANIDAT PURUSHOTTAM INTAR KALEJ MAU KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAU KAMARA N0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAU KAMARA N0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAU KAMARA N0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAU KAMARA N0-4</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAUSADA MAJARA MAU</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY @CH PAHA MAJARA MAU</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PATOR'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALURAMAPURAVA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHATAR'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SHAVAPUR MAJARA SESASAB U KARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MANAKUVॉR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAKARA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY /CHAVALAHA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY /CHAVALAHA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY @TALAUL'</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY CH6DAI MAJARA @TALAUL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KOTARA KHAGHBHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADHAVA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADHAVA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PURAB PATAI KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PURAB PATAI KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN PICCHAM PATAI</t>
+  </si>
+  <si>
+    <t>PURV MADHYAMIK V YALAY B.RAYARASH KALॉ</t>
+  </si>
+  <si>
+    <t>ATH MAK V YAL 7BALAHA KA PURAVA MAJARA B-RAYAR' KALAM</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B-RAYAR' KHUD</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BENIPUR PAL'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PARADAVॉ</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAHA KOTARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MURAKA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MURAKA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KURMIPURAVA MAJARA MURAKA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ARAVAR' NAU DHAYA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY OVAR'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LALAI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LODHAUTA KALॉ</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HARAD' KALॉ</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BOJH</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIL |PDAKDYAJDY</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DHAUNEHA MAJARA SEMARA</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIL JBHSHRCHADYASHRADYATHABHDYACH KDYAIBHTDYAJDY SHRCH|THABHTATHABHDYAJ</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY KHOHAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MADAHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TURAGAVAM</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HADAHA MAJARA GOIYA KHUD</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|SHR J~NAKL AI J~NAKL|AIBHTBBH SHR AIKL|PKL|AI THATHABHKL|SHRADYABBHTHATHABH AIDYAJ|BBHAIKL AIBHTBBHDYAJBH|THABHBBH|SHRCH SHRAJ|SHRCH THATHABHKL|SHR M</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH KAMARA NAM0-4</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH DHTE SHAN KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADH DHTE SHAN KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAGCHAHA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY KALAGCHAHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY J MARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MANAKA CHATAINI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY K@NAYADH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KO@NAYA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY M TAYAR MAJARA GAHUR</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY GAHUR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAI PURA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DOHDAYA MAPH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KOTAVA MAPH</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS JBH|LABHJBH|CHAJAIBH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KATAI YA DADI KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KATAI YA DADI KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LAPॉV</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AUJHAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAP TAHA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAP TAHA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NIBI KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NIBI KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GCHAJVAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LABED CHANUBHUJI MAJARA KH DEHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AJUNAPUR MAJARA KH DEHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY A HARANAPUR MAJARA KH DEHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MOHANAPUR MAJARA KH DEHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KH DEHA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KH DEHA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>MAHASHRIA BA8YAMIK INTAR KALEJ KH DEHA KAMARA NAM0- 1</t>
+  </si>
+  <si>
+    <t>MAHASHRIA BA8YAMIK INTAR KALEJ KH DEHA KAMARA NAM0- 2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAKAVA MAJARA KH DEHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAVAI KHUD</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY TE6DAV U A MAPH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NEVARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LAUR' THAM KAMARA NAM0 &amp;1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LAUR' THAM KAMARA NAM0 &amp;2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HANUMAN GAMJ MAZARA LAUR'</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS |PTHABHLABHJBH|THABHCH SHRCHADY BBHCHAJDYAJDY K|TDYADYAJDY AIDYACHAJAIBH</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHOR</t>
+  </si>
+  <si>
+    <t>SUBHASH I TAR KALEJ ITAVॉ KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>SUBHASH I TAR KALEJ ITAVॉ KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>SUBHASH I TAR KALEJ ITAVॉ KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ROKHAR' PURAVA MAZARA ITAVAM</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAHU LAYA PURAVA MAZARA ITAVA.C</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY 7BAS=DHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAPUR</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY GHUNAVA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DE VADHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LODHAURA</t>
+  </si>
+  <si>
+    <t>PURV MADHYAMIK V YALAY LODHAURA</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY DE VARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KH DE VARAMAPH</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY RAMANAGAR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PUV MA Y MAK V YALAY RAMANAGAR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MOHANI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PURA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KARAH'</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY JORAVARA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DE VIPUR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B SAMHA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RE (VA</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DE VANI MAJARA BUDHAVAL</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NONAMAI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAHADI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAKHARAVAR</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BॉDHI KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BॉDHI KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAPURI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAIPURA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAIPURA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAIPURA KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARAHAT</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAHORAKHAS</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ARAVARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAGAREHI DVITIY</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LALAPUR MAJARA BAGAREHI</t>
+  </si>
+  <si>
+    <t>KRRISHAK INTAR KALEJ BHAURI KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>KRRISHAK INTAR KALEJ BHAURI KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>KRRISHAK INTAR KALEJ BHAURI KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>KRRISHAK INTAR KALEJ BHAURI KAMARA NAM0-4</t>
+  </si>
+  <si>
+    <t>KRRISHAK INTAR KALEJ BHAURI KAMARA NAM0-5</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BIRU KA PURAVA SITHAT GHARAGHANA PURAVA MAJARA BHAURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUDAUHA MAJARA BHAURI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BYUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 VYUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAMAPUR TARAUMHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KOTHILIHARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAGHAUDA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHOH KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHOH KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 REHUTIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SEMARIYA CHARANADASI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHITALAPUR TARAUHA</t>
+  </si>
+  <si>
+    <t>TYAGI INTAR KALEJ AIMCHAVARA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>TYAGI INTAR KALEJ AIMCHAVARA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAUGHATA MAJARA AIMCHAVARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHARAUDH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAGAT SIMH KA PURAVA MAJARA KHARAUDH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SEMARADAHA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SEMARADAHA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHAMCHA KA PURAVA SEMARADAHA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 CHAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASAVANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHARADAHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PAVARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAYA CHANDRA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AGARAHUNDA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AGARAHUNDA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AGARAHUNDA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GIRADHARA KA PURAVA MAJARA AGARAHUNDA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UDAKI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAUDHIYAMAPHI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KAUBARA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KAUBARA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 POKHARI MAJARA KAUBARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARACHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAURIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GADHACHAPA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GADHACHAPA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHERIHARI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PATERIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HANUVA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HANUVA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GADARIYAN PURAVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAIYA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BAGAICHA PURAVA MAJARA SARAIYA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BAGAICHA PURAVA MAJARA SARAIYA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSILAM PURAVA MAJARA SARAIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMPURIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHANDRAMARA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHANDRAMARA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 CHANDRAMARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GADAKHAN MAJARA CHANDRAMARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAHILAPURAVA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAHILAPURAVA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KARKA PADARIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUKAMAKHURD KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUKAMAKHURD KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAILAHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHOTI MADAIYAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SEHARIN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BANIDHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BADI MADAIYAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KOLAGADAHIYA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KOLAGADAHIYA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KACHAR PURAVA MAJARA KOLAGADAHIYA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PAHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIDDHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BANADI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUKAMABUJURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAPAHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAUBASTA MAJARA RUKAMABUJURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAKHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAMKAPURAVA MAJARA DADARIMAPHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHOTI BELAHARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TIKARIYA JAMUNAHARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANAGAVAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BADIPATIN MAJARA IMTAVA DUDAILA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DUDAULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IMTAVA DUDAILA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAGARAHA KOLAN MAJARA IMTAVA DUDAILA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 IMTAVA DUDAILA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 IMTAVA DUDAILA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAMIYA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 DODAMAPHI SITHAT DOMDAKHAS</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MARAKUNDI SITHAT KIHUNIYAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MARAKUNDI PRATHAM SITHAT KIHUNIYAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAVIN KIHUNIYAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AMACHUR NERUVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHERIHAKHURD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHERIHA BUJURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAROMAPHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GOPIPUR MAJARA KARAUHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KARAUHA KOLAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARAHAMAPHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DAMDI KOLAN MAJARA BARAHAMAPHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHULHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMAPUR KALYANAGADH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHESHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KALYANAPUR KHAS</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAGAR MAJARA KALYANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAKSHMANAPUR MAJARA KALYANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARADIDAMDI MAJARA KALYANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NIHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAGADARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HELA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHIACHARI</t>
+  </si>
+  <si>
+    <t>ADARSH INTAR KALEJ MANIKAPUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>ADARSH INTAR KALEJ MANIKAPUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>ADARSH INTAR KALEJ MANIKAPUR KAMARA NAM0-3</t>
+  </si>
+  <si>
+    <t>ADARSH INTAR KALEJ MANIKAPUR KAMARA NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANIKAPUR PRATHAM KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANIKAPUR PRATHAM KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>RAJAKIY BALIKA INTAR KAJEL MANIKAPUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>RAJAKIY BALIKA INTAR KAJEL MANIKAPUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANIKAPUR DVITIY</t>
+  </si>
+  <si>
+    <t>KANYA PU0MA0VI0 MANIKAPUR KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>KANYA PU0MA0VI0 MANIKAPUR KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>KANYA PRA0VI0 MANIKAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAHAT KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAHAT KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SUKHARAMAPUR MAJARA CHUREHAKESHARUVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARIJANAPUR MAJARA CHUREHAKESHARUVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KEKARAMAR MAJARA CHUREHAKESHARUVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GURAULA MAJARA CHUREHAKESHARUVA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 DARARI MAJARA CHUREHAKESHARUVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIMGAVA KOTA KANDAILA KAMARA NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIMGAVA KOTA KANDAILA KAMARA NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UCHADIH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TEDHAVA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAMARAUHA MAJARA UCHADIH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AILAHA BADHAIYA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SAKARAUHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAUGURADARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GIDURAHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR KALYANAGADH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
   </si>
   <si>
     <t>COMPOSITE VIDYALAY RANIPUR KALYANGADH ROOM NO-2</t>
@@ -737,8 +1409,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -754,7 +1434,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -762,12 +1442,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1066,82 +1764,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>442</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>444</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>445</v>
       </c>
       <c r="G2" t="s">
-        <v>222</v>
+        <v>446</v>
       </c>
       <c r="H2" t="s">
-        <v>223</v>
+        <v>447</v>
       </c>
       <c r="I2" t="s">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="J2" t="s">
-        <v>225</v>
+        <v>449</v>
       </c>
       <c r="K2" t="s">
-        <v>226</v>
+        <v>450</v>
       </c>
       <c r="L2" t="s">
-        <v>227</v>
+        <v>451</v>
       </c>
       <c r="M2" t="s">
-        <v>228</v>
+        <v>452</v>
       </c>
       <c r="N2" t="s">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="O2" t="s">
-        <v>230</v>
+        <v>454</v>
       </c>
       <c r="P2" t="s">
-        <v>231</v>
+        <v>455</v>
       </c>
       <c r="Q2" t="s">
-        <v>232</v>
+        <v>456</v>
       </c>
       <c r="R2" t="s">
-        <v>233</v>
+        <v>457</v>
       </c>
       <c r="S2" t="s">
-        <v>234</v>
+        <v>458</v>
       </c>
       <c r="T2" t="s">
-        <v>235</v>
+        <v>459</v>
       </c>
       <c r="U2" t="s">
-        <v>236</v>
+        <v>460</v>
       </c>
       <c r="V2" t="s">
-        <v>236</v>
+        <v>460</v>
       </c>
       <c r="W2" t="s">
-        <v>237</v>
+        <v>461</v>
       </c>
       <c r="X2" t="s">
-        <v>238</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1149,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1163</v>
@@ -1223,7 +1990,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>638</v>
@@ -1297,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>717</v>
@@ -1371,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>979</v>
@@ -1445,7 +2212,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>1119</v>
@@ -1519,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>1209</v>
@@ -1593,7 +2360,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1233</v>
@@ -1667,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1192</v>
@@ -1741,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>928</v>
@@ -1815,7 +2582,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>732</v>
@@ -1889,7 +2656,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>850</v>
@@ -1963,7 +2730,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>851</v>
@@ -2037,7 +2804,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>1051</v>
@@ -2111,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1027</v>
@@ -2185,7 +2952,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>658</v>
@@ -2259,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>797</v>
@@ -2333,7 +3100,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>988</v>
@@ -2407,7 +3174,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>869</v>
@@ -2481,7 +3248,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>1144</v>
@@ -2555,7 +3322,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>1084</v>
@@ -2629,7 +3396,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>1074</v>
@@ -2703,7 +3470,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>707</v>
@@ -2777,7 +3544,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>433</v>
@@ -2851,7 +3618,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>802</v>
@@ -2925,7 +3692,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>797</v>
@@ -2999,7 +3766,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>741</v>
@@ -3073,7 +3840,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>728</v>
@@ -3147,7 +3914,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>833</v>
@@ -3221,7 +3988,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>965</v>
@@ -3295,7 +4062,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>509</v>
@@ -3369,7 +4136,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>956</v>
@@ -3443,7 +4210,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>767</v>
@@ -3517,7 +4284,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>662</v>
@@ -3591,7 +4358,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>644</v>
@@ -3665,7 +4432,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>1104</v>
@@ -3739,7 +4506,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>821</v>
@@ -3813,7 +4580,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>566</v>
@@ -3887,7 +4654,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>549</v>
@@ -3961,7 +4728,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>1094</v>
@@ -4035,7 +4802,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>894</v>
@@ -4109,7 +4876,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>782</v>
@@ -4183,7 +4950,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>555</v>
@@ -4257,7 +5024,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>621</v>
@@ -4331,7 +5098,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>1163</v>
@@ -4405,7 +5172,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>896</v>
@@ -4479,7 +5246,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>703</v>
@@ -4553,7 +5320,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>1004</v>
@@ -4627,7 +5394,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>1074</v>
@@ -4701,7 +5468,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>951</v>
@@ -4775,7 +5542,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>781</v>
@@ -4849,7 +5616,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>731</v>
@@ -4923,7 +5690,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>701</v>
@@ -4997,7 +5764,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>516</v>
@@ -5071,7 +5838,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>1166</v>
@@ -5145,7 +5912,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>395</v>
@@ -5219,7 +5986,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>834</v>
@@ -5293,7 +6060,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>741</v>
@@ -5367,7 +6134,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>338</v>
@@ -5441,7 +6208,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>747</v>
@@ -5515,7 +6282,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>813</v>
@@ -5589,7 +6356,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>613</v>
@@ -5663,7 +6430,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>1028</v>
@@ -5737,7 +6504,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>1189</v>
@@ -5811,7 +6578,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>978</v>
@@ -5885,7 +6652,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>734</v>
@@ -5959,7 +6726,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>487</v>
@@ -6033,7 +6800,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>1085</v>
@@ -6107,7 +6874,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>1126</v>
@@ -6181,7 +6948,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>546</v>
@@ -6255,7 +7022,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>632</v>
@@ -6329,7 +7096,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>652</v>
@@ -6403,7 +7170,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>758</v>
@@ -6477,7 +7244,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>821</v>
@@ -6551,7 +7318,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>689</v>
@@ -6625,7 +7392,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>1162</v>
@@ -6699,7 +7466,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>1197</v>
@@ -6773,7 +7540,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>1065</v>
@@ -6847,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>626</v>
@@ -6921,7 +7688,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>626</v>
@@ -6995,7 +7762,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>1033</v>
@@ -7069,7 +7836,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>728</v>
@@ -7143,7 +7910,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>718</v>
@@ -7217,7 +7984,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>877</v>
@@ -7291,7 +8058,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>456</v>
@@ -7365,7 +8132,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>797</v>
@@ -7439,7 +8206,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>596</v>
@@ -7513,7 +8280,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>801</v>
@@ -7587,7 +8354,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>655</v>
@@ -7661,7 +8428,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>663</v>
@@ -7735,7 +8502,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>545</v>
@@ -7809,7 +8576,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>1102</v>
@@ -7883,7 +8650,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>979</v>
@@ -7957,7 +8724,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>855</v>
@@ -8031,7 +8798,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>504</v>
@@ -8105,7 +8872,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>685</v>
@@ -8179,7 +8946,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>690</v>
@@ -8253,7 +9020,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>979</v>
@@ -8327,7 +9094,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>516</v>
@@ -8401,7 +9168,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>490</v>
@@ -8475,7 +9242,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>732</v>
@@ -8549,7 +9316,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>995</v>
@@ -8623,7 +9390,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>666</v>
@@ -8697,7 +9464,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>491</v>
@@ -8771,7 +9538,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>645</v>
@@ -8845,7 +9612,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>787</v>
@@ -8919,7 +9686,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>1120</v>
@@ -8993,7 +9760,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>1039</v>
@@ -9067,7 +9834,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>1175</v>
@@ -9141,7 +9908,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>1139</v>
@@ -9215,7 +9982,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>770</v>
@@ -9289,7 +10056,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>792</v>
@@ -9363,7 +10130,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>1069</v>
@@ -9437,7 +10204,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>879</v>
@@ -9511,7 +10278,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>946</v>
@@ -9585,7 +10352,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>954</v>
@@ -9659,7 +10426,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>937</v>
@@ -9733,7 +10500,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>539</v>
@@ -9807,7 +10574,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>644</v>
@@ -9881,7 +10648,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>838</v>
@@ -9955,7 +10722,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>1157</v>
@@ -10029,7 +10796,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>1214</v>
@@ -10103,7 +10870,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>654</v>
@@ -10177,7 +10944,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>566</v>
@@ -10251,7 +11018,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>956</v>
@@ -10325,7 +11092,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>928</v>
@@ -10399,7 +11166,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>871</v>
@@ -10473,7 +11240,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>635</v>
@@ -10547,7 +11314,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>678</v>
@@ -10621,7 +11388,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>678</v>
@@ -10695,7 +11462,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>834</v>
@@ -10769,7 +11536,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>695</v>
@@ -10843,7 +11610,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>852</v>
@@ -10917,7 +11684,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>694</v>
@@ -10991,7 +11758,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>1212</v>
@@ -11065,7 +11832,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>925</v>
@@ -11139,7 +11906,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>543</v>
@@ -11213,7 +11980,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>1117</v>
@@ -11287,7 +12054,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1128</v>
@@ -11361,7 +12128,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>37</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>538</v>
@@ -11435,7 +12202,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>366</v>
@@ -11509,7 +12276,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>734</v>
@@ -11583,7 +12350,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>702</v>
@@ -11657,7 +12424,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>1027</v>
@@ -11731,7 +12498,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>944</v>
@@ -11805,7 +12572,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>835</v>
@@ -11879,7 +12646,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>884</v>
@@ -11953,7 +12720,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>503</v>
@@ -12027,7 +12794,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>680</v>
@@ -12101,7 +12868,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>339</v>
@@ -12175,7 +12942,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>758</v>
@@ -12249,7 +13016,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>857</v>
@@ -12323,7 +13090,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>879</v>
@@ -12397,7 +13164,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>994</v>
@@ -12471,7 +13238,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>1120</v>
@@ -12545,7 +13312,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>985</v>
@@ -12619,7 +13386,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>841</v>
@@ -12693,7 +13460,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>660</v>
@@ -12767,7 +13534,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>661</v>
@@ -12841,7 +13608,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>689</v>
@@ -12915,7 +13682,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>895</v>
@@ -12989,7 +13756,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>701</v>
@@ -13063,7 +13830,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>1050</v>
@@ -13137,7 +13904,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>978</v>
@@ -13211,7 +13978,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>974</v>
@@ -13285,7 +14052,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>822</v>
@@ -13359,7 +14126,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>1032</v>
@@ -13433,7 +14200,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>779</v>
@@ -13507,7 +14274,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>1114</v>
@@ -13581,7 +14348,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>787</v>
@@ -13655,7 +14422,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>514</v>
@@ -13729,7 +14496,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>605</v>
@@ -13803,7 +14570,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>705</v>
@@ -13877,7 +14644,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>812</v>
@@ -13951,7 +14718,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>726</v>
@@ -14025,7 +14792,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>659</v>
@@ -14099,7 +14866,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>601</v>
@@ -14173,7 +14940,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>529</v>
@@ -14247,7 +15014,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>22</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>1152</v>
@@ -14321,7 +15088,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>1199</v>
@@ -14395,7 +15162,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>1055</v>
@@ -14469,7 +15236,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>776</v>
@@ -14543,7 +15310,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>1118</v>
@@ -14617,7 +15384,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>970</v>
@@ -14691,7 +15458,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>699</v>
@@ -14765,7 +15532,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>759</v>
@@ -14839,7 +15606,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>638</v>
@@ -14913,7 +15680,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>100</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>652</v>
@@ -14987,7 +15754,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>1078</v>
@@ -15061,7 +15828,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>663</v>
@@ -15135,7 +15902,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>1063</v>
@@ -15209,7 +15976,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>1178</v>
@@ -15283,7 +16050,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>1119</v>
@@ -15357,7 +16124,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>1060</v>
@@ -15431,7 +16198,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>703</v>
@@ -15505,7 +16272,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>113</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>734</v>
@@ -15579,7 +16346,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>867</v>
@@ -15653,7 +16420,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>870</v>
@@ -15727,7 +16494,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>9</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>796</v>
@@ -15801,7 +16568,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>763</v>
@@ -15875,7 +16642,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>645</v>
@@ -15949,7 +16716,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>928</v>
@@ -16023,7 +16790,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>111</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>1063</v>
@@ -16097,7 +16864,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>801</v>
@@ -16171,7 +16938,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>577</v>
@@ -16245,7 +17012,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>658</v>
@@ -16319,7 +17086,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>1088</v>
@@ -16393,7 +17160,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>969</v>
@@ -16467,7 +17234,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>1137</v>
@@ -16541,7 +17308,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>377</v>
@@ -16615,7 +17382,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>44</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>880</v>
@@ -16689,7 +17456,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="C213">
         <v>1045</v>
@@ -16763,7 +17530,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="C214">
         <v>780</v>
@@ -16837,7 +17604,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="C215">
         <v>1180</v>
@@ -16911,7 +17678,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="C216">
         <v>762</v>
@@ -16985,7 +17752,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>1078</v>
@@ -17059,7 +17826,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>34</v>
+        <v>241</v>
       </c>
       <c r="C218">
         <v>467</v>
@@ -17133,7 +17900,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>242</v>
       </c>
       <c r="C219">
         <v>1027</v>
@@ -17207,7 +17974,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="C220">
         <v>407</v>
@@ -17281,7 +18048,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="C221">
         <v>815</v>
@@ -17355,7 +18122,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="C222">
         <v>677</v>
@@ -17429,7 +18196,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>726</v>
@@ -17503,7 +18270,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="C224">
         <v>944</v>
@@ -17577,7 +18344,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="C225">
         <v>712</v>
@@ -17651,7 +18418,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>22</v>
+        <v>249</v>
       </c>
       <c r="C226">
         <v>931</v>
@@ -17725,7 +18492,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="C227">
         <v>374</v>
@@ -17799,7 +18566,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="C228">
         <v>1093</v>
@@ -17873,7 +18640,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -17947,7 +18714,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
       <c r="C230">
         <v>929</v>
@@ -18021,7 +18788,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="C231">
         <v>820</v>
@@ -18095,7 +18862,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="C232">
         <v>768</v>
@@ -18169,7 +18936,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>578</v>
@@ -18243,7 +19010,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="C234">
         <v>919</v>
@@ -18317,7 +19084,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>674</v>
@@ -18391,7 +19158,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="C236">
         <v>678</v>
@@ -18465,7 +19232,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>106</v>
+        <v>260</v>
       </c>
       <c r="C237">
         <v>462</v>
@@ -18539,7 +19306,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>16</v>
+        <v>261</v>
       </c>
       <c r="C238">
         <v>459</v>
@@ -18613,7 +19380,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="C239">
         <v>769</v>
@@ -18687,7 +19454,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>27</v>
+        <v>263</v>
       </c>
       <c r="C240">
         <v>997</v>
@@ -18761,7 +19528,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c r="C241">
         <v>1231</v>
@@ -18835,7 +19602,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>134</v>
+        <v>265</v>
       </c>
       <c r="C242">
         <v>918</v>
@@ -18909,7 +19676,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>16</v>
+        <v>266</v>
       </c>
       <c r="C243">
         <v>474</v>
@@ -18983,7 +19750,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>135</v>
+        <v>267</v>
       </c>
       <c r="C244">
         <v>910</v>
@@ -19057,7 +19824,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="C245">
         <v>1086</v>
@@ -19131,7 +19898,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="C246">
         <v>960</v>
@@ -19205,7 +19972,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="C247">
         <v>943</v>
@@ -19279,7 +20046,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="C248">
         <v>443</v>
@@ -19353,7 +20120,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="C249">
         <v>1034</v>
@@ -19427,7 +20194,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>44</v>
+        <v>273</v>
       </c>
       <c r="C250">
         <v>639</v>
@@ -19501,7 +20268,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="C251">
         <v>947</v>
@@ -19575,7 +20342,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="C252">
         <v>1096</v>
@@ -19649,7 +20416,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
       <c r="C253">
         <v>374</v>
@@ -19723,7 +20490,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="C254">
         <v>893</v>
@@ -19797,7 +20564,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>140</v>
+        <v>278</v>
       </c>
       <c r="C255">
         <v>1017</v>
@@ -19871,7 +20638,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="C256">
         <v>1108</v>
@@ -19945,7 +20712,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="C257">
         <v>749</v>
@@ -20019,7 +20786,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="C258">
         <v>811</v>
@@ -20093,7 +20860,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>142</v>
+        <v>282</v>
       </c>
       <c r="C259">
         <v>1102</v>
@@ -20167,7 +20934,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>143</v>
+        <v>283</v>
       </c>
       <c r="C260">
         <v>1123</v>
@@ -20241,7 +21008,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="C261">
         <v>658</v>
@@ -20315,7 +21082,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="C262">
         <v>932</v>
@@ -20389,7 +21156,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>94</v>
+        <v>286</v>
       </c>
       <c r="C263">
         <v>1059</v>
@@ -20463,7 +21230,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c r="C264">
         <v>852</v>
@@ -20537,7 +21304,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>16</v>
+        <v>288</v>
       </c>
       <c r="C265">
         <v>625</v>
@@ -20611,7 +21378,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="C266">
         <v>694</v>
@@ -20685,7 +21452,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="C267">
         <v>1209</v>
@@ -20759,7 +21526,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>145</v>
+        <v>291</v>
       </c>
       <c r="C268">
         <v>800</v>
@@ -20833,7 +21600,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>110</v>
+        <v>292</v>
       </c>
       <c r="C269">
         <v>1109</v>
@@ -20907,7 +21674,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>146</v>
+        <v>293</v>
       </c>
       <c r="C270">
         <v>1177</v>
@@ -20981,7 +21748,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>147</v>
+        <v>294</v>
       </c>
       <c r="C271">
         <v>672</v>
@@ -21055,7 +21822,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>147</v>
+        <v>295</v>
       </c>
       <c r="C272">
         <v>664</v>
@@ -21129,7 +21896,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>148</v>
+        <v>296</v>
       </c>
       <c r="C273">
         <v>1082</v>
@@ -21203,7 +21970,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>148</v>
+        <v>297</v>
       </c>
       <c r="C274">
         <v>613</v>
@@ -21277,7 +22044,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>148</v>
+        <v>298</v>
       </c>
       <c r="C275">
         <v>651</v>
@@ -21351,7 +22118,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>149</v>
+        <v>299</v>
       </c>
       <c r="C276">
         <v>583</v>
@@ -21425,7 +22192,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C277">
         <v>816</v>
@@ -21499,7 +22266,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C278">
         <v>466</v>
@@ -21573,7 +22340,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>151</v>
+        <v>302</v>
       </c>
       <c r="C279">
         <v>991</v>
@@ -21647,7 +22414,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>152</v>
+        <v>303</v>
       </c>
       <c r="C280">
         <v>683</v>
@@ -21721,7 +22488,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>104</v>
+        <v>304</v>
       </c>
       <c r="C281">
         <v>941</v>
@@ -21795,7 +22562,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="C282">
         <v>808</v>
@@ -21869,7 +22636,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="C283">
         <v>912</v>
@@ -21943,7 +22710,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="C284">
         <v>659</v>
@@ -22017,7 +22784,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>155</v>
+        <v>308</v>
       </c>
       <c r="C285">
         <v>601</v>
@@ -22091,7 +22858,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>156</v>
+        <v>309</v>
       </c>
       <c r="C286">
         <v>364</v>
@@ -22165,7 +22932,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="C287">
         <v>891</v>
@@ -22239,7 +23006,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>16</v>
+        <v>311</v>
       </c>
       <c r="C288">
         <v>593</v>
@@ -22313,7 +23080,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="C289">
         <v>951</v>
@@ -22387,7 +23154,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="C290">
         <v>483</v>
@@ -22461,7 +23228,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>158</v>
+        <v>314</v>
       </c>
       <c r="C291">
         <v>988</v>
@@ -22535,7 +23302,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>159</v>
+        <v>315</v>
       </c>
       <c r="C292">
         <v>1146</v>
@@ -22609,7 +23376,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>160</v>
+        <v>316</v>
       </c>
       <c r="C293">
         <v>902</v>
@@ -22683,7 +23450,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>161</v>
+        <v>317</v>
       </c>
       <c r="C294">
         <v>388</v>
@@ -22757,7 +23524,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="C295">
         <v>705</v>
@@ -22831,7 +23598,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="C296">
         <v>976</v>
@@ -22905,7 +23672,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="C297">
         <v>1014</v>
@@ -22979,7 +23746,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="C298">
         <v>927</v>
@@ -23053,7 +23820,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>162</v>
+        <v>322</v>
       </c>
       <c r="C299">
         <v>981</v>
@@ -23127,7 +23894,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="C300">
         <v>530</v>
@@ -23201,7 +23968,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>324</v>
       </c>
       <c r="C301">
         <v>1175</v>
@@ -23275,7 +24042,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="C302">
         <v>1190</v>
@@ -23349,7 +24116,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>150</v>
+        <v>326</v>
       </c>
       <c r="C303">
         <v>1170</v>
@@ -23423,7 +24190,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="C304">
         <v>596</v>
@@ -23497,7 +24264,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="C305">
         <v>889</v>
@@ -23571,7 +24338,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>165</v>
+        <v>329</v>
       </c>
       <c r="C306">
         <v>675</v>
@@ -23645,7 +24412,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>163</v>
+        <v>330</v>
       </c>
       <c r="C307">
         <v>1051</v>
@@ -23719,7 +24486,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>150</v>
+        <v>331</v>
       </c>
       <c r="C308">
         <v>1105</v>
@@ -23793,7 +24560,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="C309">
         <v>772</v>
@@ -23867,7 +24634,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>25</v>
+        <v>333</v>
       </c>
       <c r="C310">
         <v>637</v>
@@ -23941,7 +24708,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="C311">
         <v>614</v>
@@ -24015,7 +24782,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>166</v>
+        <v>335</v>
       </c>
       <c r="C312">
         <v>1014</v>
@@ -24089,7 +24856,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>167</v>
+        <v>336</v>
       </c>
       <c r="C313">
         <v>793</v>
@@ -24163,7 +24930,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="C314">
         <v>668</v>
@@ -24237,7 +25004,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>110</v>
+        <v>338</v>
       </c>
       <c r="C315">
         <v>722</v>
@@ -24311,7 +25078,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>168</v>
+        <v>339</v>
       </c>
       <c r="C316">
         <v>579</v>
@@ -24385,7 +25152,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>169</v>
+        <v>340</v>
       </c>
       <c r="C317">
         <v>789</v>
@@ -24459,7 +25226,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>170</v>
+        <v>341</v>
       </c>
       <c r="C318">
         <v>800</v>
@@ -24533,7 +25300,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="C319">
         <v>564</v>
@@ -24607,7 +25374,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>172</v>
+        <v>343</v>
       </c>
       <c r="C320">
         <v>884</v>
@@ -24681,7 +25448,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="C321">
         <v>712</v>
@@ -24755,7 +25522,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>173</v>
+        <v>345</v>
       </c>
       <c r="C322">
         <v>572</v>
@@ -24829,7 +25596,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="C323">
         <v>807</v>
@@ -24903,7 +25670,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>175</v>
+        <v>347</v>
       </c>
       <c r="C324">
         <v>1107</v>
@@ -24977,7 +25744,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>29</v>
+        <v>348</v>
       </c>
       <c r="C325">
         <v>659</v>
@@ -25051,7 +25818,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>30</v>
+        <v>349</v>
       </c>
       <c r="C326">
         <v>651</v>
@@ -25125,7 +25892,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="C327">
         <v>862</v>
@@ -25199,7 +25966,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
       <c r="C328">
         <v>795</v>
@@ -25273,7 +26040,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>352</v>
       </c>
       <c r="C329">
         <v>711</v>
@@ -25347,7 +26114,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>118</v>
+        <v>353</v>
       </c>
       <c r="C330">
         <v>1137</v>
@@ -25421,7 +26188,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>176</v>
+        <v>354</v>
       </c>
       <c r="C331">
         <v>1024</v>
@@ -25495,7 +26262,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>176</v>
+        <v>355</v>
       </c>
       <c r="C332">
         <v>1005</v>
@@ -25569,7 +26336,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>177</v>
+        <v>356</v>
       </c>
       <c r="C333">
         <v>593</v>
@@ -25643,7 +26410,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="C334">
         <v>616</v>
@@ -25717,7 +26484,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="C335">
         <v>617</v>
@@ -25791,7 +26558,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>110</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>1072</v>
@@ -25865,7 +26632,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>994</v>
@@ -25939,7 +26706,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>178</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>742</v>
@@ -26013,7 +26780,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>785</v>
@@ -26087,7 +26854,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>179</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>957</v>
@@ -26161,7 +26928,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>614</v>
@@ -26235,7 +27002,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>1070</v>
@@ -26309,7 +27076,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>181</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>639</v>
@@ -26383,7 +27150,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>182</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>672</v>
@@ -26457,7 +27224,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>832</v>
@@ -26531,7 +27298,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>491</v>
@@ -26605,7 +27372,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>9</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>509</v>
@@ -26679,7 +27446,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>10</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>704</v>
@@ -26753,7 +27520,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>183</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>1051</v>
@@ -26827,7 +27594,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>15</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>631</v>
@@ -26901,7 +27668,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>184</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>587</v>
@@ -26975,7 +27742,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>544</v>
@@ -27049,7 +27816,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>778</v>
@@ -27123,7 +27890,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>185</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>845</v>
@@ -27197,7 +27964,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>914</v>
@@ -27271,7 +28038,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>186</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>746</v>
@@ -27345,7 +28112,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>187</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>826</v>
@@ -27419,7 +28186,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>946</v>
@@ -27493,7 +28260,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>159</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>437</v>
@@ -27567,7 +28334,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>188</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>1084</v>
@@ -27641,7 +28408,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>173</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>1086</v>
@@ -27715,7 +28482,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>189</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>775</v>
@@ -27789,7 +28556,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>190</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>713</v>
@@ -27863,7 +28630,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>191</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>300</v>
@@ -27937,7 +28704,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>192</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>768</v>
@@ -28011,7 +28778,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>193</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>1095</v>
@@ -28085,7 +28852,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>512</v>
@@ -28159,7 +28926,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>192</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>981</v>
@@ -28233,7 +29000,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>195</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>618</v>
@@ -28307,7 +29074,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>15</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>420</v>
@@ -28381,7 +29148,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>196</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>700</v>
@@ -28455,7 +29222,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>197</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>728</v>
@@ -28529,7 +29296,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>34</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>312</v>
@@ -28603,7 +29370,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>198</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>365</v>
@@ -28677,7 +29444,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>199</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>628</v>
@@ -28751,7 +29518,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>200</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>657</v>
@@ -28825,7 +29592,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>198</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>555</v>
@@ -28899,7 +29666,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>28</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>991</v>
@@ -28973,7 +29740,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>16</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>974</v>
@@ -29047,7 +29814,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>28</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>768</v>
@@ -29121,7 +29888,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>28</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>622</v>
@@ -29195,7 +29962,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>906</v>
@@ -29269,7 +30036,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>201</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>999</v>
@@ -29343,7 +30110,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>201</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>1047</v>
@@ -29417,7 +30184,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>202</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>965</v>
@@ -29491,7 +30258,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>203</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>1007</v>
@@ -29565,7 +30332,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>204</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>1002</v>
@@ -29639,7 +30406,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>204</v>
+        <v>411</v>
       </c>
       <c r="C388">
         <v>1034</v>
@@ -29713,7 +30480,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>205</v>
+        <v>412</v>
       </c>
       <c r="C389">
         <v>490</v>
@@ -29787,7 +30554,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>206</v>
+        <v>413</v>
       </c>
       <c r="C390">
         <v>697</v>
@@ -29861,7 +30628,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>158</v>
+        <v>414</v>
       </c>
       <c r="C391">
         <v>1094</v>
@@ -29935,7 +30702,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="C392">
         <v>1057</v>
@@ -30009,7 +30776,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>160</v>
+        <v>416</v>
       </c>
       <c r="C393">
         <v>1023</v>
@@ -30083,7 +30850,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>207</v>
+        <v>417</v>
       </c>
       <c r="C394">
         <v>959</v>
@@ -30157,7 +30924,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>55</v>
+        <v>418</v>
       </c>
       <c r="C395">
         <v>954</v>
@@ -30231,7 +30998,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>56</v>
+        <v>419</v>
       </c>
       <c r="C396">
         <v>884</v>
@@ -30305,7 +31072,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>208</v>
+        <v>420</v>
       </c>
       <c r="C397">
         <v>794</v>
@@ -30379,7 +31146,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>209</v>
+        <v>421</v>
       </c>
       <c r="C398">
         <v>567</v>
@@ -30453,7 +31220,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>209</v>
+        <v>422</v>
       </c>
       <c r="C399">
         <v>630</v>
@@ -30527,7 +31294,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>210</v>
+        <v>423</v>
       </c>
       <c r="C400">
         <v>853</v>
@@ -30601,7 +31368,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>211</v>
+        <v>424</v>
       </c>
       <c r="C401">
         <v>618</v>
@@ -30675,7 +31442,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>212</v>
+        <v>425</v>
       </c>
       <c r="C402">
         <v>723</v>
@@ -30749,7 +31516,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>34</v>
+        <v>426</v>
       </c>
       <c r="C403">
         <v>461</v>
@@ -30823,7 +31590,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>213</v>
+        <v>427</v>
       </c>
       <c r="C404">
         <v>1109</v>
@@ -30897,7 +31664,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>214</v>
+        <v>428</v>
       </c>
       <c r="C405">
         <v>981</v>
@@ -30971,7 +31738,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>164</v>
+        <v>429</v>
       </c>
       <c r="C406">
         <v>628</v>
@@ -31045,7 +31812,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>165</v>
+        <v>430</v>
       </c>
       <c r="C407">
         <v>719</v>
@@ -31119,7 +31886,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>16</v>
+        <v>431</v>
       </c>
       <c r="C408">
         <v>410</v>
@@ -31193,7 +31960,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>28</v>
+        <v>432</v>
       </c>
       <c r="C409">
         <v>799</v>
@@ -31267,7 +32034,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>215</v>
+        <v>433</v>
       </c>
       <c r="C410">
         <v>1024</v>
@@ -31341,7 +32108,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>55</v>
+        <v>434</v>
       </c>
       <c r="C411">
         <v>995</v>
@@ -31415,7 +32182,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>56</v>
+        <v>435</v>
       </c>
       <c r="C412">
         <v>419</v>
@@ -31489,7 +32256,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>58</v>
+        <v>436</v>
       </c>
       <c r="C413">
         <v>704</v>
@@ -31563,7 +32330,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>59</v>
+        <v>437</v>
       </c>
       <c r="C414">
         <v>745</v>
@@ -31637,7 +32404,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>110</v>
+        <v>438</v>
       </c>
       <c r="C415">
         <v>761</v>
@@ -31711,7 +32478,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>34</v>
+        <v>439</v>
       </c>
       <c r="C416">
         <v>706</v>
@@ -31785,7 +32552,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>216</v>
+        <v>440</v>
       </c>
       <c r="C417">
         <v>777</v>
@@ -31859,7 +32626,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>217</v>
+        <v>441</v>
       </c>
       <c r="C418">
         <v>745</v>
